--- a/BCEndlineNgay (22)_Empty.xlsx
+++ b/BCEndlineNgay (22)_Empty.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leuti\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leuti\Desktop\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D5A7FA-C520-42EB-98AC-F20682AC2E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A1F3DF-4757-44A8-B5C4-087A32205DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1023,14 +1023,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>201231</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>181421</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/BCEndlineNgay (22)_Empty.xlsx
+++ b/BCEndlineNgay (22)_Empty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leuti\Desktop\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A1F3DF-4757-44A8-B5C4-087A32205DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7287325-03F2-486E-8017-7B0693F3A1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="14">
   <si>
     <t>VIKING VIETNAMCO.LTD</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Code:BM11/QT 13/CL01
 Revison:01
 Issued date:10/10/2024</t>
-  </si>
-  <si>
-    <t>Daisy</t>
   </si>
   <si>
     <t>Ngày
@@ -94,79 +91,6 @@
   <si>
     <t>Tổng</t>
   </si>
-  <si>
-    <t>LSX:... -- MH: ...</t>
-  </si>
-  <si>
-    <r>
-      <t>Mã Hàng/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Style:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>…</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CHUYỀN/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Line:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>…</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -176,7 +100,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,28 +184,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1412,18 +1314,8 @@
       <c r="R3" s="2"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="E5" s="4"/>
       <c r="I5" s="4"/>
       <c r="K5" s="4"/>
       <c r="R5" s="3"/>
@@ -1433,28 +1325,28 @@
     </row>
     <row r="7" spans="1:21" ht="33.6" customHeight="1">
       <c r="A7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>4</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>5</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
@@ -1463,52 +1355,52 @@
     <row r="8" spans="1:21" ht="35.25" customHeight="1">
       <c r="A8" s="14"/>
       <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="F8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="J8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="N8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="P8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1518,40 +1410,40 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1561,40 +1453,40 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1604,40 +1496,40 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1647,40 +1539,40 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1690,40 +1582,40 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1733,45 +1625,45 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6">
         <f>SUM(B9:B14)</f>
@@ -1786,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="6">
         <f>SUM(F9:F14)</f>
@@ -1801,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="6">
         <f>SUM(J9:J14)</f>
@@ -1816,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N15" s="6">
         <f>SUM(N9:N14)</f>
@@ -1831,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/BCEndlineNgay (22)_Empty.xlsx
+++ b/BCEndlineNgay (22)_Empty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leuti\Desktop\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7287325-03F2-486E-8017-7B0693F3A1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50EE84D-8147-44C7-AFAB-2E579EB7FD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="18">
   <si>
     <t>VIKING VIETNAMCO.LTD</t>
   </si>
@@ -91,6 +91,64 @@
   <si>
     <t>Tổng</t>
   </si>
+  <si>
+    <r>
+      <t>Mã Hàng/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Style:</t>
+    </r>
+  </si>
+  <si>
+    <t>LSX:752 -- MH: 0088 342 29 V0.3</t>
+  </si>
+  <si>
+    <r>
+      <t>CHUYỀN/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Line:</t>
+    </r>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
 </sst>
 </file>
 
@@ -100,7 +158,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +242,28 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1231,7 +1311,7 @@
     <col min="3" max="3" width="30.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="31.125" style="1" customWidth="1"/>
@@ -1314,8 +1394,18 @@
       <c r="R3" s="2"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="K5" s="4"/>
       <c r="R5" s="3"/>
